--- a/data/trans_dic/P24D-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 35,72</t>
+          <t>18,48; 35,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,19; 75,07</t>
+          <t>59,53; 75,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,38; 71,32</t>
+          <t>52,7; 72,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,2; 58,11</t>
+          <t>31,43; 58,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 25,82</t>
+          <t>6,96; 25,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,97; 73,49</t>
+          <t>52,83; 73,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,11; 67,72</t>
+          <t>45,65; 68,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,58; 59,98</t>
+          <t>38,87; 59,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,35</t>
+          <t>16,44; 28,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,34; 72,14</t>
+          <t>59,48; 72,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,41; 67,35</t>
+          <t>52,11; 67,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,02; 56,34</t>
+          <t>37,44; 54,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,3; 41,51</t>
+          <t>26,97; 42,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,19; 57,79</t>
+          <t>43,52; 58,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,67; 25,76</t>
+          <t>14,5; 25,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,94; 51,38</t>
+          <t>29,58; 52,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 50,76</t>
+          <t>32,42; 51,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,52; 51,83</t>
+          <t>35,6; 51,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 35,27</t>
+          <t>19,41; 34,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,42; 53,14</t>
+          <t>34,31; 52,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,48; 42,61</t>
+          <t>31,46; 43,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,1; 53,36</t>
+          <t>41,8; 52,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,25; 27,15</t>
+          <t>18,26; 27,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,88; 49,57</t>
+          <t>34,67; 49,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,99; 26,35</t>
+          <t>13,67; 26,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,28; 47,82</t>
+          <t>30,46; 47,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,9; 46,1</t>
+          <t>27,3; 46,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 51,16</t>
+          <t>29,54; 52,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 38,26</t>
+          <t>20,81; 39,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,43; 66,83</t>
+          <t>45,95; 68,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,18; 59,85</t>
+          <t>38,48; 60,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,28; 62,69</t>
+          <t>42,04; 63,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 28,88</t>
+          <t>17,71; 28,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,42; 53,64</t>
+          <t>38,97; 52,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,9; 50,1</t>
+          <t>35,39; 49,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,87; 53,41</t>
+          <t>37,65; 53,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 37,11</t>
+          <t>23,2; 37,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,56; 55,82</t>
+          <t>37,31; 55,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,04; 71,15</t>
+          <t>55,17; 71,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 53,29</t>
+          <t>23,31; 52,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,6; 49,48</t>
+          <t>31,01; 49,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,46; 77,63</t>
+          <t>58,32; 76,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,95; 61,27</t>
+          <t>41,72; 62,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,8; 52,58</t>
+          <t>29,5; 52,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,11; 39,71</t>
+          <t>27,53; 39,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,47; 62,32</t>
+          <t>48,69; 62,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,64; 65,87</t>
+          <t>52,4; 65,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,53; 47,92</t>
+          <t>30,24; 47,93</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,16; 45,77</t>
+          <t>25,46; 44,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,69; 64,39</t>
+          <t>43,23; 64,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,66; 59,26</t>
+          <t>38,09; 60,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,2</t>
+          <t>0,0; 11,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,47; 51,94</t>
+          <t>25,21; 51,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,93; 63,81</t>
+          <t>40,55; 65,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,06; 66,0</t>
+          <t>39,99; 65,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 22,78</t>
+          <t>6,34; 22,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,21; 43,05</t>
+          <t>27,49; 43,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,17; 61,74</t>
+          <t>44,11; 61,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,63; 57,75</t>
+          <t>42,31; 58,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 14,22</t>
+          <t>3,88; 13,9</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,06; 43,21</t>
+          <t>25,65; 43,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,89; 64,13</t>
+          <t>42,67; 64,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,67; 58,14</t>
+          <t>36,02; 56,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,57; 34,48</t>
+          <t>15,82; 33,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,8; 46,46</t>
+          <t>23,53; 46,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,33; 68,21</t>
+          <t>44,18; 69,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,05; 44,47</t>
+          <t>21,39; 44,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,87; 38,03</t>
+          <t>18,05; 38,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,84; 42,1</t>
+          <t>27,92; 41,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47,12; 64,09</t>
+          <t>46,79; 63,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,09; 48,53</t>
+          <t>32,92; 48,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 32,31</t>
+          <t>18,91; 32,34</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,87; 43,21</t>
+          <t>29,8; 41,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,19; 44,77</t>
+          <t>32,53; 44,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,78; 42,99</t>
+          <t>29,06; 43,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,29; 60,57</t>
+          <t>39,37; 59,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,44; 51,11</t>
+          <t>35,14; 50,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,9; 57,32</t>
+          <t>42,12; 56,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,74; 46,64</t>
+          <t>31,42; 46,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,33; 61,56</t>
+          <t>46,68; 61,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,53; 43,62</t>
+          <t>33,63; 43,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,45; 47,82</t>
+          <t>38,04; 47,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,59</t>
+          <t>32,2; 42,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,67; 57,71</t>
+          <t>45,16; 58,24</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,08; 35,08</t>
+          <t>24,16; 34,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,89; 45,49</t>
+          <t>33,87; 46,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,11; 54,03</t>
+          <t>40,74; 53,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,5; 29,27</t>
+          <t>17,24; 29,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,71; 37,96</t>
+          <t>24,56; 38,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,13; 46,74</t>
+          <t>31,95; 46,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,82; 59,11</t>
+          <t>45,81; 59,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,71; 46,66</t>
+          <t>31,44; 47,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,21; 34,38</t>
+          <t>25,74; 34,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,98; 44,17</t>
+          <t>34,91; 43,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44,81; 54,0</t>
+          <t>44,55; 53,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,31; 33,53</t>
+          <t>23,92; 33,47</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,83; 32,93</t>
+          <t>28,05; 33,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,71; 49,11</t>
+          <t>43,54; 49,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,76; 45,48</t>
+          <t>40,02; 45,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31,66; 39,42</t>
+          <t>31,84; 39,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,9; 38,21</t>
+          <t>31,47; 37,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,22; 54,72</t>
+          <t>47,87; 54,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,95; 47,67</t>
+          <t>41,21; 47,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40,4; 47,24</t>
+          <t>40,08; 47,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,06; 34,34</t>
+          <t>30,02; 33,97</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45,96; 50,42</t>
+          <t>46,33; 50,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41,38; 45,8</t>
+          <t>41,37; 45,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36,3; 41,83</t>
+          <t>36,2; 41,63</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20978; 40491</t>
+          <t>20951; 40295</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79419; 102461</t>
+          <t>81251; 102538</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55694; 75831</t>
+          <t>56036; 77415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26316; 49012</t>
+          <t>26507; 49119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4575; 18120</t>
+          <t>4886; 17641</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51872; 71965</t>
+          <t>51735; 71611</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33250; 49922</t>
+          <t>33652; 50174</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25738; 39006</t>
+          <t>25279; 38865</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29623; 53872</t>
+          <t>30174; 52879</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139096; 169105</t>
+          <t>139429; 169663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94368; 121254</t>
+          <t>93819; 121263</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55303; 84159</t>
+          <t>55931; 81879</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52271; 79492</t>
+          <t>51649; 80871</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87796; 120273</t>
+          <t>90567; 120876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30676; 53840</t>
+          <t>30321; 53908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38456; 65978</t>
+          <t>37985; 67093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39618; 60225</t>
+          <t>38472; 60786</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53713; 78378</t>
+          <t>53833; 78312</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28565; 49673</t>
+          <t>27343; 48740</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33712; 52056</t>
+          <t>33612; 51675</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97635; 132167</t>
+          <t>97566; 133357</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>151259; 191726</t>
+          <t>150207; 189065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63849; 94993</t>
+          <t>63895; 95309</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78957; 112216</t>
+          <t>78474; 112390</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20542; 38682</t>
+          <t>20063; 39248</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39733; 60751</t>
+          <t>38692; 60425</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25912; 44412</t>
+          <t>26295; 44826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21716; 37967</t>
+          <t>21926; 38783</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18828; 35932</t>
+          <t>19538; 36742</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38039; 55960</t>
+          <t>38477; 57306</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31077; 48722</t>
+          <t>31320; 49087</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26899; 39885</t>
+          <t>26749; 40285</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43528; 69508</t>
+          <t>42617; 68773</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83076; 113056</t>
+          <t>82129; 111677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63805; 89050</t>
+          <t>62896; 88249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52194; 73623</t>
+          <t>51902; 73297</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38509; 62901</t>
+          <t>39324; 63224</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48723; 72424</t>
+          <t>48408; 72042</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75268; 99109</t>
+          <t>76842; 99461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17535; 39513</t>
+          <t>17281; 38792</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31082; 50257</t>
+          <t>31497; 50224</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60785; 80718</t>
+          <t>60640; 79202</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45629; 66631</t>
+          <t>45379; 67875</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20916; 38190</t>
+          <t>21430; 38067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76198; 107660</t>
+          <t>74638; 106097</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115624; 145650</t>
+          <t>113792; 145044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>128102; 163385</t>
+          <t>129980; 161892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43351; 70330</t>
+          <t>44390; 70356</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21217; 38593</t>
+          <t>21469; 37232</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39014; 58855</t>
+          <t>39516; 58754</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32060; 50448</t>
+          <t>32424; 51262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3783</t>
+          <t>0; 3986</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15162; 30916</t>
+          <t>15006; 30513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26784; 41758</t>
+          <t>26538; 42697</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22125; 37382</t>
+          <t>22650; 37164</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1948; 6802</t>
+          <t>1894; 6696</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39150; 61923</t>
+          <t>39543; 61862</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70841; 96831</t>
+          <t>69185; 96022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57601; 81868</t>
+          <t>59991; 83106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2730; 9045</t>
+          <t>2470; 8846</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33648; 53737</t>
+          <t>31892; 53475</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35918; 53704</t>
+          <t>35732; 53990</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32354; 51299</t>
+          <t>31777; 50122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12436; 25881</t>
+          <t>11873; 25368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14821; 30199</t>
+          <t>15298; 30173</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29650; 45618</t>
+          <t>29548; 46228</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16108; 32489</t>
+          <t>15628; 32816</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8592; 18284</t>
+          <t>8677; 18304</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52723; 79724</t>
+          <t>52876; 78525</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70973; 96539</t>
+          <t>70468; 94972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53370; 78270</t>
+          <t>53100; 78607</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22888; 39784</t>
+          <t>23281; 39817</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>70178; 101545</t>
+          <t>70012; 98476</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92673; 125026</t>
+          <t>90837; 124251</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56628; 84566</t>
+          <t>57163; 85737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69710; 104802</t>
+          <t>68112; 102232</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>56851; 81989</t>
+          <t>56367; 81722</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80988; 110788</t>
+          <t>81413; 109598</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53257; 80813</t>
+          <t>54441; 80443</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>69529; 92381</t>
+          <t>70048; 92220</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>132588; 172470</t>
+          <t>132982; 170401</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>181689; 225973</t>
+          <t>179721; 225776</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119813; 157564</t>
+          <t>119137; 157448</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>144336; 186464</t>
+          <t>145898; 188156</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76096; 110863</t>
+          <t>76339; 110515</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>100364; 134713</t>
+          <t>100309; 136270</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>104867; 137816</t>
+          <t>103908; 136233</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32165; 53810</t>
+          <t>31693; 54016</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45764; 70311</t>
+          <t>45484; 71128</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66426; 96626</t>
+          <t>66061; 96281</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98188; 126670</t>
+          <t>98159; 126905</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>36592; 55595</t>
+          <t>37465; 56181</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>131400; 172324</t>
+          <t>129012; 171782</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>175937; 222143</t>
+          <t>175584; 219605</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>210333; 253430</t>
+          <t>209101; 253061</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>73671; 101594</t>
+          <t>72478; 101404</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>384310; 454734</t>
+          <t>387290; 456308</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>590891; 663949</t>
+          <t>588595; 664147</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>467578; 534850</t>
+          <t>470680; 539975</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>261761; 325962</t>
+          <t>263266; 325930</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>272592; 326520</t>
+          <t>268931; 323551</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>467390; 530327</t>
+          <t>463910; 527689</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>377594; 439527</t>
+          <t>379914; 442177</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>261133; 305334</t>
+          <t>259098; 304949</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>671967; 767700</t>
+          <t>671062; 759321</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1066822; 1170387</t>
+          <t>1075336; 1178002</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>868127; 960933</t>
+          <t>868049; 964351</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>534770; 616261</t>
+          <t>533230; 613310</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P24D-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 35,55</t>
+          <t>17,96; 35,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,53; 75,13</t>
+          <t>58,89; 75,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,7; 72,81</t>
+          <t>51,75; 72,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,43; 58,24</t>
+          <t>34,99; 57,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 25,14</t>
+          <t>6,85; 26,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,83; 73,12</t>
+          <t>53,24; 74,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,65; 68,07</t>
+          <t>45,06; 67,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,87; 59,76</t>
+          <t>39,47; 57,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 28,81</t>
+          <t>15,87; 27,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,48; 72,38</t>
+          <t>59,42; 72,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,11; 67,35</t>
+          <t>52,31; 67,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,44; 54,81</t>
+          <t>39,08; 54,83</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,97; 42,23</t>
+          <t>27,4; 41,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,52; 58,08</t>
+          <t>42,4; 57,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,5; 25,79</t>
+          <t>14,57; 25,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,58; 52,24</t>
+          <t>29,04; 50,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,42; 51,23</t>
+          <t>31,61; 50,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,6; 51,79</t>
+          <t>35,23; 52,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,41; 34,6</t>
+          <t>18,94; 33,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 52,76</t>
+          <t>34,61; 51,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 43,0</t>
+          <t>31,34; 42,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41,8; 52,62</t>
+          <t>42,06; 53,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,26; 27,24</t>
+          <t>18,18; 27,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 49,65</t>
+          <t>33,46; 48,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 26,74</t>
+          <t>13,46; 26,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,46; 47,56</t>
+          <t>30,52; 48,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,3; 46,53</t>
+          <t>26,54; 46,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,54; 52,26</t>
+          <t>29,1; 51,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 39,13</t>
+          <t>20,42; 38,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,95; 68,44</t>
+          <t>44,78; 67,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,48; 60,3</t>
+          <t>38,81; 59,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,04; 63,32</t>
+          <t>42,2; 62,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 28,57</t>
+          <t>18,1; 28,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,97; 52,99</t>
+          <t>39,5; 53,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,39; 49,65</t>
+          <t>34,77; 49,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,65; 53,18</t>
+          <t>38,45; 53,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,2; 37,3</t>
+          <t>22,98; 37,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,31; 55,53</t>
+          <t>37,77; 55,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,17; 71,41</t>
+          <t>54,01; 72,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 52,32</t>
+          <t>24,26; 53,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,01; 49,44</t>
+          <t>30,56; 49,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,32; 76,17</t>
+          <t>58,37; 77,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,72; 62,41</t>
+          <t>42,12; 62,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,5; 52,41</t>
+          <t>29,23; 52,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,53; 39,14</t>
+          <t>28,21; 39,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,69; 62,06</t>
+          <t>49,55; 62,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,4; 65,27</t>
+          <t>51,26; 64,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,24; 47,93</t>
+          <t>30,13; 49,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,46; 44,15</t>
+          <t>24,48; 44,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,23; 64,28</t>
+          <t>42,45; 64,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,09; 60,22</t>
+          <t>38,39; 59,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,8</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,21; 51,26</t>
+          <t>25,65; 49,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,55; 65,25</t>
+          <t>40,48; 65,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,99; 65,61</t>
+          <t>39,78; 65,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 22,43</t>
+          <t>5,45; 22,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,49; 43,0</t>
+          <t>28,0; 42,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,11; 61,22</t>
+          <t>45,63; 61,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,31; 58,62</t>
+          <t>42,18; 59,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,9</t>
+          <t>3,8; 13,3</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,65; 43,0</t>
+          <t>26,51; 42,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,67; 64,47</t>
+          <t>42,91; 64,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,02; 56,81</t>
+          <t>36,21; 58,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,82; 33,8</t>
+          <t>15,99; 34,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,53; 46,42</t>
+          <t>22,36; 46,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,18; 69,12</t>
+          <t>44,53; 68,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,39; 44,92</t>
+          <t>22,13; 44,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,05; 38,07</t>
+          <t>17,27; 37,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,92; 41,47</t>
+          <t>27,61; 41,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,79; 63,05</t>
+          <t>47,26; 63,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,92; 48,74</t>
+          <t>32,2; 47,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,91; 32,34</t>
+          <t>18,69; 32,21</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,8; 41,91</t>
+          <t>28,86; 41,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,53; 44,5</t>
+          <t>32,46; 44,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 43,58</t>
+          <t>29,17; 43,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,37; 59,09</t>
+          <t>43,59; 59,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,14; 50,94</t>
+          <t>35,59; 52,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,12; 56,71</t>
+          <t>42,34; 57,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,42; 46,43</t>
+          <t>31,03; 46,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,68; 61,45</t>
+          <t>48,81; 63,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,63; 43,1</t>
+          <t>33,33; 43,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,04; 47,78</t>
+          <t>38,28; 47,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32,2; 42,55</t>
+          <t>32,51; 42,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,16; 58,24</t>
+          <t>48,28; 59,61</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,16; 34,97</t>
+          <t>24,28; 34,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,87; 46,01</t>
+          <t>33,74; 45,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,74; 53,41</t>
+          <t>40,23; 52,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,24; 29,38</t>
+          <t>17,63; 29,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,56; 38,4</t>
+          <t>25,1; 38,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,95; 46,57</t>
+          <t>31,95; 46,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,81; 59,22</t>
+          <t>46,06; 59,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,44; 47,15</t>
+          <t>30,67; 45,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,74; 34,27</t>
+          <t>25,88; 33,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,67</t>
+          <t>35,25; 44,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44,55; 53,92</t>
+          <t>44,61; 54,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,92; 33,47</t>
+          <t>24,78; 34,39</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,05; 33,05</t>
+          <t>28,03; 33,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,54; 49,13</t>
+          <t>43,47; 49,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,02; 45,91</t>
+          <t>40,02; 45,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31,84; 39,42</t>
+          <t>31,92; 39,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,47; 37,87</t>
+          <t>31,4; 37,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,87; 54,45</t>
+          <t>47,64; 54,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,21; 47,96</t>
+          <t>41,41; 47,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40,08; 47,18</t>
+          <t>40,3; 46,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,02; 33,97</t>
+          <t>30,15; 34,1</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46,33; 50,75</t>
+          <t>45,98; 50,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41,37; 45,96</t>
+          <t>41,47; 45,84</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36,2; 41,63</t>
+          <t>36,86; 41,98</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>35003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32226</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>66630</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20951; 40295</t>
+          <t>20362; 40425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81251; 102538</t>
+          <t>80378; 102418</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56036; 77415</t>
+          <t>55029; 76824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26507; 49119</t>
+          <t>26576; 44014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4886; 17641</t>
+          <t>4804; 18542</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51735; 71611</t>
+          <t>52138; 72494</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33652; 50174</t>
+          <t>33213; 50120</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25279; 38865</t>
+          <t>26184; 38356</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30174; 52879</t>
+          <t>29124; 51360</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139429; 169663</t>
+          <t>139283; 170374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93819; 121263</t>
+          <t>94182; 121453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55931; 81879</t>
+          <t>55606; 78017</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51953</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42875</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94829</t>
+          <t>95153</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51649; 80871</t>
+          <t>52473; 79023</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90567; 120876</t>
+          <t>88231; 119474</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30321; 53908</t>
+          <t>30461; 53793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37985; 67093</t>
+          <t>38361; 66279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38472; 60786</t>
+          <t>37512; 59632</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53833; 78312</t>
+          <t>53268; 78630</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27343; 48740</t>
+          <t>26673; 47636</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33612; 51675</t>
+          <t>35120; 52510</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97566; 133357</t>
+          <t>97213; 131492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>150207; 189065</t>
+          <t>151121; 191848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63895; 95309</t>
+          <t>63618; 96149</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78474; 112390</t>
+          <t>78151; 113162</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62839</t>
+          <t>65338</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20063; 39248</t>
+          <t>19752; 38765</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38692; 60425</t>
+          <t>38775; 61112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26295; 44826</t>
+          <t>25565; 44878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21926; 38783</t>
+          <t>23149; 41036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19538; 36742</t>
+          <t>19175; 36174</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38477; 57306</t>
+          <t>37495; 56311</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31320; 49087</t>
+          <t>31593; 48680</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26749; 40285</t>
+          <t>27018; 40318</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42617; 68773</t>
+          <t>43576; 68405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82129; 111677</t>
+          <t>83254; 111875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62896; 88249</t>
+          <t>61791; 88168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51902; 73297</t>
+          <t>55202; 76211</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>66370</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39324; 63224</t>
+          <t>38954; 62759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48408; 72042</t>
+          <t>49006; 72218</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76842; 99461</t>
+          <t>75223; 100558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17281; 38792</t>
+          <t>21792; 48125</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31497; 50224</t>
+          <t>31045; 50009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60640; 79202</t>
+          <t>60700; 80839</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45379; 67875</t>
+          <t>45810; 67727</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21430; 38067</t>
+          <t>23150; 41578</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74638; 106097</t>
+          <t>76469; 106364</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113792; 145044</t>
+          <t>115803; 146589</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129980; 161892</t>
+          <t>127150; 159932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44390; 70356</t>
+          <t>50921; 83183</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5530</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21469; 37232</t>
+          <t>20646; 37321</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39516; 58754</t>
+          <t>38803; 58788</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32424; 51262</t>
+          <t>32685; 50574</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3986</t>
+          <t>0; 4842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15006; 30513</t>
+          <t>15271; 29598</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26538; 42697</t>
+          <t>26490; 43079</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22650; 37164</t>
+          <t>22534; 37253</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1894; 6696</t>
+          <t>1752; 7089</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39543; 61862</t>
+          <t>40281; 61782</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69185; 96022</t>
+          <t>71564; 96891</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59991; 83106</t>
+          <t>59807; 84335</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2470; 8846</t>
+          <t>2785; 9746</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>31373</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31892; 53475</t>
+          <t>32965; 53033</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35732; 53990</t>
+          <t>35929; 54159</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31777; 50122</t>
+          <t>31948; 51306</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11873; 25368</t>
+          <t>12148; 26277</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15298; 30173</t>
+          <t>14539; 29993</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29548; 46228</t>
+          <t>29782; 46114</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15628; 32816</t>
+          <t>16169; 32463</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8677; 18304</t>
+          <t>8443; 18552</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52876; 78525</t>
+          <t>52291; 77932</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70468; 94972</t>
+          <t>71186; 95883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53100; 78607</t>
+          <t>51935; 76433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23281; 39817</t>
+          <t>23336; 40217</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>97516</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>195607</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>70012; 98476</t>
+          <t>67823; 98460</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90837; 124251</t>
+          <t>90639; 123694</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57163; 85737</t>
+          <t>57378; 85778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68112; 102232</t>
+          <t>82901; 113708</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>56367; 81722</t>
+          <t>57093; 83527</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81413; 109598</t>
+          <t>81827; 110679</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54441; 80443</t>
+          <t>53772; 80414</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>70048; 92220</t>
+          <t>84718; 109438</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>132982; 170401</t>
+          <t>131801; 171253</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179721; 225776</t>
+          <t>180863; 222248</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119137; 157448</t>
+          <t>120295; 158211</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>145898; 188156</t>
+          <t>175625; 216843</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>49202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>51660</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87245</t>
+          <t>100863</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76339; 110515</t>
+          <t>76742; 108335</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>100309; 136270</t>
+          <t>99914; 134775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>103908; 136233</t>
+          <t>102606; 134775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31693; 54016</t>
+          <t>36956; 61639</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45484; 71128</t>
+          <t>46494; 71871</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66061; 96281</t>
+          <t>66064; 95430</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98159; 126905</t>
+          <t>98693; 127732</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>37465; 56181</t>
+          <t>41502; 62234</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>129012; 171782</t>
+          <t>129736; 169425</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>175584; 219605</t>
+          <t>177289; 223648</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>209101; 253061</t>
+          <t>209390; 255032</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>72478; 101404</t>
+          <t>85466; 118623</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>291294</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>626863</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>387290; 456308</t>
+          <t>387022; 457836</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>588595; 664147</t>
+          <t>587726; 662984</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>470680; 539975</t>
+          <t>470649; 540294</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>263266; 325930</t>
+          <t>285482; 353950</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>268931; 323551</t>
+          <t>268296; 324646</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>463910; 527689</t>
+          <t>461690; 528034</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>379914; 442177</t>
+          <t>381797; 441009</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>259098; 304949</t>
+          <t>282477; 329045</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>671062; 759321</t>
+          <t>673899; 762196</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1075336; 1178002</t>
+          <t>1067264; 1169235</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>868049; 964351</t>
+          <t>870043; 961813</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>533230; 613310</t>
+          <t>588102; 669762</t>
         </is>
       </c>
     </row>
